--- a/Collections/EURO/San_Marino/#EURO#San_Marino#Regular#[2002-present]#circulation_quality.xlsx
+++ b/Collections/EURO/San_Marino/#EURO#San_Marino#Regular#[2002-present]#circulation_quality.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\EURO\San_Marino\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90A98F21-6DBC-4D00-85FC-5AD3F90453DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34D27683-DD96-40CF-99D3-4F2A8704BEFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="2280" windowWidth="33150" windowHeight="17700" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1cent" sheetId="4" r:id="rId1"/>
@@ -2251,7 +2251,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F23 F21 F25">
+  <conditionalFormatting sqref="F21 F23 F25">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2877,7 +2877,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F23 F21 F25">
+  <conditionalFormatting sqref="F21 F23 F25">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3503,7 +3503,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F23 F21 F25">
+  <conditionalFormatting sqref="F21 F23 F25">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4209,7 +4209,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F23 F21 F26">
+  <conditionalFormatting sqref="F21 F23 F26">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4883,7 +4883,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F23 F21">
+  <conditionalFormatting sqref="F21 F23">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5591,7 +5591,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F23 F21">
+  <conditionalFormatting sqref="F21 F23">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6293,7 +6293,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F23 F21">
+  <conditionalFormatting sqref="F21 F23">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -7003,7 +7003,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F23 F21">
+  <conditionalFormatting sqref="F21 F23">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
